--- a/tracker-cartera-fede.xlsx
+++ b/tracker-cartera-fede.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="$#,##0;($#,##0);-"/>
     <numFmt numFmtId="165" formatCode="0.0%;(0.0%);-"/>
-    <numFmt numFmtId="166" formatCode="u$s #,##0;(u$s #,##0);-"/>
+    <numFmt numFmtId="166" formatCode="&quot;u$s&quot; #,##0;(&quot;u$s&quot; #,##0);-"/>
   </numFmts>
   <fonts count="8">
     <font>
